--- a/public_administration_forms/019_decision_review_application_form--public_administration_forms.xlsx
+++ b/public_administration_forms/019_decision_review_application_form--public_administration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'review_and_approve',_'value':_'review_and_approve'}</t>
+          <t>review_and_approve</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Review and Approve', 'value': 'Review and Approve'}</t>
+          <t>Review and Approve</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'send_for_review',_'value':_'send_for_review'}</t>
+          <t>send_for_review</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Send for Review', 'value': 'Send for Review'}</t>
+          <t>Send for Review</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'revoke',_'value':_'revoke'}</t>
+          <t>revoke</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Revoke', 'value': 'Revoke'}</t>
+          <t>Revoke</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'complete',_'value':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Complete', 'value': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled', 'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
